--- a/GetLucky_Pro_Forma_v2.xlsx
+++ b/GetLucky_Pro_Forma_v2.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D48"/>
+  <dimension ref="B2:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="2" max="2"/>
@@ -1177,6 +1177,64 @@
         <is>
           <t>48 months from Jan 2026</t>
         </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>BLENDED STRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Insured swings included in the membership</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>A CAPPED allowance. Unlimited cannot be underwritten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Prize on an included swing ($)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Premium ceded on the membership (% of sub)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Fair price for the included swings at the same target loss ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Get Lucky share of membership</t>
+        </is>
+      </c>
+      <c r="C54">
+        <f>1-C53</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:CH33"/>
+  <dimension ref="B2:CH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -6473,339 +6531,339 @@
         </is>
       </c>
       <c r="C27">
-        <f>C16*Assumptions!$C$19</f>
+        <f>C16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D27">
-        <f>D16*Assumptions!$C$19</f>
+        <f>D16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="E27">
-        <f>E16*Assumptions!$C$19</f>
+        <f>E16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="F27">
-        <f>F16*Assumptions!$C$19</f>
+        <f>F16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="G27">
-        <f>G16*Assumptions!$C$19</f>
+        <f>G16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="H27">
-        <f>H16*Assumptions!$C$19</f>
+        <f>H16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="I27">
-        <f>I16*Assumptions!$C$19</f>
+        <f>I16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="J27">
-        <f>J16*Assumptions!$C$19</f>
+        <f>J16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="K27">
-        <f>K16*Assumptions!$C$19</f>
+        <f>K16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="L27">
-        <f>L16*Assumptions!$C$19</f>
+        <f>L16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="M27">
-        <f>M16*Assumptions!$C$19</f>
+        <f>M16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="N27">
-        <f>N16*Assumptions!$C$19</f>
+        <f>N16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="O27">
-        <f>O16*Assumptions!$C$19</f>
+        <f>O16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="P27">
-        <f>P16*Assumptions!$C$19</f>
+        <f>P16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>Q16*Assumptions!$C$19</f>
+        <f>Q16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="R27">
-        <f>R16*Assumptions!$C$19</f>
+        <f>R16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="S27">
-        <f>S16*Assumptions!$C$19</f>
+        <f>S16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="T27">
-        <f>T16*Assumptions!$C$19</f>
+        <f>T16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="U27">
-        <f>U16*Assumptions!$C$19</f>
+        <f>U16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="V27">
-        <f>V16*Assumptions!$C$19</f>
+        <f>V16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="W27">
-        <f>W16*Assumptions!$C$19</f>
+        <f>W16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="X27">
-        <f>X16*Assumptions!$C$19</f>
+        <f>X16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>Y16*Assumptions!$C$19</f>
+        <f>Y16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="Z27">
-        <f>Z16*Assumptions!$C$19</f>
+        <f>Z16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>AA16*Assumptions!$C$19</f>
+        <f>AA16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>AB16*Assumptions!$C$19</f>
+        <f>AB16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>AC16*Assumptions!$C$19</f>
+        <f>AC16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>AD16*Assumptions!$C$19</f>
+        <f>AD16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>AE16*Assumptions!$C$19</f>
+        <f>AE16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AF27">
-        <f>AF16*Assumptions!$C$19</f>
+        <f>AF16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AG27">
-        <f>AG16*Assumptions!$C$19</f>
+        <f>AG16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AH27">
-        <f>AH16*Assumptions!$C$19</f>
+        <f>AH16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AI27">
-        <f>AI16*Assumptions!$C$19</f>
+        <f>AI16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AJ27">
-        <f>AJ16*Assumptions!$C$19</f>
+        <f>AJ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AK27">
-        <f>AK16*Assumptions!$C$19</f>
+        <f>AK16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AL27">
-        <f>AL16*Assumptions!$C$19</f>
+        <f>AL16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AM27">
-        <f>AM16*Assumptions!$C$19</f>
+        <f>AM16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AN27">
-        <f>AN16*Assumptions!$C$19</f>
+        <f>AN16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AO27">
-        <f>AO16*Assumptions!$C$19</f>
+        <f>AO16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AP27">
-        <f>AP16*Assumptions!$C$19</f>
+        <f>AP16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AQ27">
-        <f>AQ16*Assumptions!$C$19</f>
+        <f>AQ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AR27">
-        <f>AR16*Assumptions!$C$19</f>
+        <f>AR16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AS27">
-        <f>AS16*Assumptions!$C$19</f>
+        <f>AS16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AT27">
-        <f>AT16*Assumptions!$C$19</f>
+        <f>AT16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AU27">
-        <f>AU16*Assumptions!$C$19</f>
+        <f>AU16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AV27">
-        <f>AV16*Assumptions!$C$19</f>
+        <f>AV16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AW27">
-        <f>AW16*Assumptions!$C$19</f>
+        <f>AW16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AX27">
-        <f>AX16*Assumptions!$C$19</f>
+        <f>AX16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AY27">
-        <f>AY16*Assumptions!$C$19</f>
+        <f>AY16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AZ27">
-        <f>AZ16*Assumptions!$C$19</f>
+        <f>AZ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BA27">
-        <f>BA16*Assumptions!$C$19</f>
+        <f>BA16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BB27">
-        <f>BB16*Assumptions!$C$19</f>
+        <f>BB16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BC27">
-        <f>BC16*Assumptions!$C$19</f>
+        <f>BC16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BD27">
-        <f>BD16*Assumptions!$C$19</f>
+        <f>BD16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BE27">
-        <f>BE16*Assumptions!$C$19</f>
+        <f>BE16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BF27">
-        <f>BF16*Assumptions!$C$19</f>
+        <f>BF16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BG27">
-        <f>BG16*Assumptions!$C$19</f>
+        <f>BG16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BH27">
-        <f>BH16*Assumptions!$C$19</f>
+        <f>BH16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BI27">
-        <f>BI16*Assumptions!$C$19</f>
+        <f>BI16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BJ27">
-        <f>BJ16*Assumptions!$C$19</f>
+        <f>BJ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BK27">
-        <f>BK16*Assumptions!$C$19</f>
+        <f>BK16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BL27">
-        <f>BL16*Assumptions!$C$19</f>
+        <f>BL16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BM27">
-        <f>BM16*Assumptions!$C$19</f>
+        <f>BM16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BN27">
-        <f>BN16*Assumptions!$C$19</f>
+        <f>BN16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BO27">
-        <f>BO16*Assumptions!$C$19</f>
+        <f>BO16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BP27">
-        <f>BP16*Assumptions!$C$19</f>
+        <f>BP16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BQ27">
-        <f>BQ16*Assumptions!$C$19</f>
+        <f>BQ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BR27">
-        <f>BR16*Assumptions!$C$19</f>
+        <f>BR16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BS27">
-        <f>BS16*Assumptions!$C$19</f>
+        <f>BS16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BT27">
-        <f>BT16*Assumptions!$C$19</f>
+        <f>BT16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BU27">
-        <f>BU16*Assumptions!$C$19</f>
+        <f>BU16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BV27">
-        <f>BV16*Assumptions!$C$19</f>
+        <f>BV16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BW27">
-        <f>BW16*Assumptions!$C$19</f>
+        <f>BW16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BX27">
-        <f>BX16*Assumptions!$C$19</f>
+        <f>BX16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BY27">
-        <f>BY16*Assumptions!$C$19</f>
+        <f>BY16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BZ27">
-        <f>BZ16*Assumptions!$C$19</f>
+        <f>BZ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CA27">
-        <f>CA16*Assumptions!$C$19</f>
+        <f>CA16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CB27">
-        <f>CB16*Assumptions!$C$19</f>
+        <f>CB16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CC27">
-        <f>CC16*Assumptions!$C$19</f>
+        <f>CC16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CD27">
-        <f>CD16*Assumptions!$C$19</f>
+        <f>CD16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CE27">
-        <f>CE16*Assumptions!$C$19</f>
+        <f>CE16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CF27">
-        <f>CF16*Assumptions!$C$19</f>
+        <f>CF16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CG27">
-        <f>CG16*Assumptions!$C$19</f>
+        <f>CG16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CH27">
-        <f>CH16*Assumptions!$C$19</f>
+        <f>CH16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7495,6 +7553,349 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Membership premium ceded ($)</t>
+        </is>
+      </c>
+      <c r="C30">
+        <f>C16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="D30">
+        <f>D16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="E30">
+        <f>E16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="F30">
+        <f>F16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>G16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="H30">
+        <f>H16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>I16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="J30">
+        <f>J16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>K16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>L16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="M30">
+        <f>M16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>N16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="O30">
+        <f>O16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="P30">
+        <f>P16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="Q30">
+        <f>Q16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="R30">
+        <f>R16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="S30">
+        <f>S16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="T30">
+        <f>T16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="U30">
+        <f>U16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="V30">
+        <f>V16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="W30">
+        <f>W16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>X16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>Y16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>Z16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>AA16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>AB16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>AC16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>AD16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>AE16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AF30">
+        <f>AF16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AG30">
+        <f>AG16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AH30">
+        <f>AH16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AI30">
+        <f>AI16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AJ30">
+        <f>AJ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AK30">
+        <f>AK16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AL30">
+        <f>AL16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AM30">
+        <f>AM16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AN30">
+        <f>AN16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AO30">
+        <f>AO16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AP30">
+        <f>AP16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AQ30">
+        <f>AQ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AR30">
+        <f>AR16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AS30">
+        <f>AS16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AT30">
+        <f>AT16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AU30">
+        <f>AU16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AV30">
+        <f>AV16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AW30">
+        <f>AW16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AX30">
+        <f>AX16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AY30">
+        <f>AY16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AZ30">
+        <f>AZ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BA30">
+        <f>BA16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BB30">
+        <f>BB16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BC30">
+        <f>BC16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BD30">
+        <f>BD16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BE30">
+        <f>BE16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BF30">
+        <f>BF16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BG30">
+        <f>BG16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BH30">
+        <f>BH16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BI30">
+        <f>BI16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BJ30">
+        <f>BJ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BK30">
+        <f>BK16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BL30">
+        <f>BL16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BM30">
+        <f>BM16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BN30">
+        <f>BN16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BO30">
+        <f>BO16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BP30">
+        <f>BP16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BQ30">
+        <f>BQ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BR30">
+        <f>BR16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BS30">
+        <f>BS16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BT30">
+        <f>BT16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BU30">
+        <f>BU16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BV30">
+        <f>BV16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BW30">
+        <f>BW16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BX30">
+        <f>BX16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BY30">
+        <f>BY16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BZ30">
+        <f>BZ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CA30">
+        <f>CA16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CB30">
+        <f>CB16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CC30">
+        <f>CC16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CD30">
+        <f>CD16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CE30">
+        <f>CE16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CF30">
+        <f>CF16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CG30">
+        <f>CG16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CH30">
+        <f>CH16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+    </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
         <is>
@@ -7852,339 +8253,682 @@
         </is>
       </c>
       <c r="C33">
-        <f>C20*Insurance!$C$28</f>
+        <f>C20*Insurance!$C$28+C34</f>
         <v/>
       </c>
       <c r="D33">
-        <f>D20*Insurance!$C$28</f>
+        <f>D20*Insurance!$C$28+D34</f>
         <v/>
       </c>
       <c r="E33">
-        <f>E20*Insurance!$C$28</f>
+        <f>E20*Insurance!$C$28+E34</f>
         <v/>
       </c>
       <c r="F33">
-        <f>F20*Insurance!$C$28</f>
+        <f>F20*Insurance!$C$28+F34</f>
         <v/>
       </c>
       <c r="G33">
-        <f>G20*Insurance!$C$28</f>
+        <f>G20*Insurance!$C$28+G34</f>
         <v/>
       </c>
       <c r="H33">
-        <f>H20*Insurance!$C$28</f>
+        <f>H20*Insurance!$C$28+H34</f>
         <v/>
       </c>
       <c r="I33">
-        <f>I20*Insurance!$C$28</f>
+        <f>I20*Insurance!$C$28+I34</f>
         <v/>
       </c>
       <c r="J33">
-        <f>J20*Insurance!$C$28</f>
+        <f>J20*Insurance!$C$28+J34</f>
         <v/>
       </c>
       <c r="K33">
-        <f>K20*Insurance!$C$28</f>
+        <f>K20*Insurance!$C$28+K34</f>
         <v/>
       </c>
       <c r="L33">
-        <f>L20*Insurance!$C$28</f>
+        <f>L20*Insurance!$C$28+L34</f>
         <v/>
       </c>
       <c r="M33">
-        <f>M20*Insurance!$C$28</f>
+        <f>M20*Insurance!$C$28+M34</f>
         <v/>
       </c>
       <c r="N33">
-        <f>N20*Insurance!$C$28</f>
+        <f>N20*Insurance!$C$28+N34</f>
         <v/>
       </c>
       <c r="O33">
-        <f>O20*Insurance!$C$28</f>
+        <f>O20*Insurance!$C$28+O34</f>
         <v/>
       </c>
       <c r="P33">
-        <f>P20*Insurance!$C$28</f>
+        <f>P20*Insurance!$C$28+P34</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>Q20*Insurance!$C$28</f>
+        <f>Q20*Insurance!$C$28+Q34</f>
         <v/>
       </c>
       <c r="R33">
-        <f>R20*Insurance!$C$28</f>
+        <f>R20*Insurance!$C$28+R34</f>
         <v/>
       </c>
       <c r="S33">
-        <f>S20*Insurance!$C$28</f>
+        <f>S20*Insurance!$C$28+S34</f>
         <v/>
       </c>
       <c r="T33">
-        <f>T20*Insurance!$C$28</f>
+        <f>T20*Insurance!$C$28+T34</f>
         <v/>
       </c>
       <c r="U33">
-        <f>U20*Insurance!$C$28</f>
+        <f>U20*Insurance!$C$28+U34</f>
         <v/>
       </c>
       <c r="V33">
-        <f>V20*Insurance!$C$28</f>
+        <f>V20*Insurance!$C$28+V34</f>
         <v/>
       </c>
       <c r="W33">
-        <f>W20*Insurance!$C$28</f>
+        <f>W20*Insurance!$C$28+W34</f>
         <v/>
       </c>
       <c r="X33">
-        <f>X20*Insurance!$C$28</f>
+        <f>X20*Insurance!$C$28+X34</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>Y20*Insurance!$C$28</f>
+        <f>Y20*Insurance!$C$28+Y34</f>
         <v/>
       </c>
       <c r="Z33">
-        <f>Z20*Insurance!$C$28</f>
+        <f>Z20*Insurance!$C$28+Z34</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>AA20*Insurance!$C$28</f>
+        <f>AA20*Insurance!$C$28+AA34</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>AB20*Insurance!$C$28</f>
+        <f>AB20*Insurance!$C$28+AB34</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>AC20*Insurance!$C$28</f>
+        <f>AC20*Insurance!$C$28+AC34</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>AD20*Insurance!$C$28</f>
+        <f>AD20*Insurance!$C$28+AD34</f>
         <v/>
       </c>
       <c r="AE33">
-        <f>AE20*Insurance!$C$28</f>
+        <f>AE20*Insurance!$C$28+AE34</f>
         <v/>
       </c>
       <c r="AF33">
-        <f>AF20*Insurance!$C$28</f>
+        <f>AF20*Insurance!$C$28+AF34</f>
         <v/>
       </c>
       <c r="AG33">
-        <f>AG20*Insurance!$C$28</f>
+        <f>AG20*Insurance!$C$28+AG34</f>
         <v/>
       </c>
       <c r="AH33">
-        <f>AH20*Insurance!$C$28</f>
+        <f>AH20*Insurance!$C$28+AH34</f>
         <v/>
       </c>
       <c r="AI33">
-        <f>AI20*Insurance!$C$28</f>
+        <f>AI20*Insurance!$C$28+AI34</f>
         <v/>
       </c>
       <c r="AJ33">
-        <f>AJ20*Insurance!$C$28</f>
+        <f>AJ20*Insurance!$C$28+AJ34</f>
         <v/>
       </c>
       <c r="AK33">
-        <f>AK20*Insurance!$C$28</f>
+        <f>AK20*Insurance!$C$28+AK34</f>
         <v/>
       </c>
       <c r="AL33">
-        <f>AL20*Insurance!$C$28</f>
+        <f>AL20*Insurance!$C$28+AL34</f>
         <v/>
       </c>
       <c r="AM33">
-        <f>AM20*Insurance!$C$28</f>
+        <f>AM20*Insurance!$C$28+AM34</f>
         <v/>
       </c>
       <c r="AN33">
-        <f>AN20*Insurance!$C$28</f>
+        <f>AN20*Insurance!$C$28+AN34</f>
         <v/>
       </c>
       <c r="AO33">
-        <f>AO20*Insurance!$C$28</f>
+        <f>AO20*Insurance!$C$28+AO34</f>
         <v/>
       </c>
       <c r="AP33">
-        <f>AP20*Insurance!$C$28</f>
+        <f>AP20*Insurance!$C$28+AP34</f>
         <v/>
       </c>
       <c r="AQ33">
-        <f>AQ20*Insurance!$C$28</f>
+        <f>AQ20*Insurance!$C$28+AQ34</f>
         <v/>
       </c>
       <c r="AR33">
-        <f>AR20*Insurance!$C$28</f>
+        <f>AR20*Insurance!$C$28+AR34</f>
         <v/>
       </c>
       <c r="AS33">
-        <f>AS20*Insurance!$C$28</f>
+        <f>AS20*Insurance!$C$28+AS34</f>
         <v/>
       </c>
       <c r="AT33">
-        <f>AT20*Insurance!$C$28</f>
+        <f>AT20*Insurance!$C$28+AT34</f>
         <v/>
       </c>
       <c r="AU33">
-        <f>AU20*Insurance!$C$28</f>
+        <f>AU20*Insurance!$C$28+AU34</f>
         <v/>
       </c>
       <c r="AV33">
-        <f>AV20*Insurance!$C$28</f>
+        <f>AV20*Insurance!$C$28+AV34</f>
         <v/>
       </c>
       <c r="AW33">
-        <f>AW20*Insurance!$C$28</f>
+        <f>AW20*Insurance!$C$28+AW34</f>
         <v/>
       </c>
       <c r="AX33">
-        <f>AX20*Insurance!$C$28</f>
+        <f>AX20*Insurance!$C$28+AX34</f>
         <v/>
       </c>
       <c r="AY33">
-        <f>AY20*Insurance!$C$28</f>
+        <f>AY20*Insurance!$C$28+AY34</f>
         <v/>
       </c>
       <c r="AZ33">
-        <f>AZ20*Insurance!$C$28</f>
+        <f>AZ20*Insurance!$C$28+AZ34</f>
         <v/>
       </c>
       <c r="BA33">
-        <f>BA20*Insurance!$C$28</f>
+        <f>BA20*Insurance!$C$28+BA34</f>
         <v/>
       </c>
       <c r="BB33">
-        <f>BB20*Insurance!$C$28</f>
+        <f>BB20*Insurance!$C$28+BB34</f>
         <v/>
       </c>
       <c r="BC33">
-        <f>BC20*Insurance!$C$28</f>
+        <f>BC20*Insurance!$C$28+BC34</f>
         <v/>
       </c>
       <c r="BD33">
-        <f>BD20*Insurance!$C$28</f>
+        <f>BD20*Insurance!$C$28+BD34</f>
         <v/>
       </c>
       <c r="BE33">
-        <f>BE20*Insurance!$C$28</f>
+        <f>BE20*Insurance!$C$28+BE34</f>
         <v/>
       </c>
       <c r="BF33">
-        <f>BF20*Insurance!$C$28</f>
+        <f>BF20*Insurance!$C$28+BF34</f>
         <v/>
       </c>
       <c r="BG33">
-        <f>BG20*Insurance!$C$28</f>
+        <f>BG20*Insurance!$C$28+BG34</f>
         <v/>
       </c>
       <c r="BH33">
-        <f>BH20*Insurance!$C$28</f>
+        <f>BH20*Insurance!$C$28+BH34</f>
         <v/>
       </c>
       <c r="BI33">
-        <f>BI20*Insurance!$C$28</f>
+        <f>BI20*Insurance!$C$28+BI34</f>
         <v/>
       </c>
       <c r="BJ33">
-        <f>BJ20*Insurance!$C$28</f>
+        <f>BJ20*Insurance!$C$28+BJ34</f>
         <v/>
       </c>
       <c r="BK33">
-        <f>BK20*Insurance!$C$28</f>
+        <f>BK20*Insurance!$C$28+BK34</f>
         <v/>
       </c>
       <c r="BL33">
-        <f>BL20*Insurance!$C$28</f>
+        <f>BL20*Insurance!$C$28+BL34</f>
         <v/>
       </c>
       <c r="BM33">
-        <f>BM20*Insurance!$C$28</f>
+        <f>BM20*Insurance!$C$28+BM34</f>
         <v/>
       </c>
       <c r="BN33">
-        <f>BN20*Insurance!$C$28</f>
+        <f>BN20*Insurance!$C$28+BN34</f>
         <v/>
       </c>
       <c r="BO33">
-        <f>BO20*Insurance!$C$28</f>
+        <f>BO20*Insurance!$C$28+BO34</f>
         <v/>
       </c>
       <c r="BP33">
-        <f>BP20*Insurance!$C$28</f>
+        <f>BP20*Insurance!$C$28+BP34</f>
         <v/>
       </c>
       <c r="BQ33">
-        <f>BQ20*Insurance!$C$28</f>
+        <f>BQ20*Insurance!$C$28+BQ34</f>
         <v/>
       </c>
       <c r="BR33">
-        <f>BR20*Insurance!$C$28</f>
+        <f>BR20*Insurance!$C$28+BR34</f>
         <v/>
       </c>
       <c r="BS33">
-        <f>BS20*Insurance!$C$28</f>
+        <f>BS20*Insurance!$C$28+BS34</f>
         <v/>
       </c>
       <c r="BT33">
-        <f>BT20*Insurance!$C$28</f>
+        <f>BT20*Insurance!$C$28+BT34</f>
         <v/>
       </c>
       <c r="BU33">
-        <f>BU20*Insurance!$C$28</f>
+        <f>BU20*Insurance!$C$28+BU34</f>
         <v/>
       </c>
       <c r="BV33">
-        <f>BV20*Insurance!$C$28</f>
+        <f>BV20*Insurance!$C$28+BV34</f>
         <v/>
       </c>
       <c r="BW33">
-        <f>BW20*Insurance!$C$28</f>
+        <f>BW20*Insurance!$C$28+BW34</f>
         <v/>
       </c>
       <c r="BX33">
-        <f>BX20*Insurance!$C$28</f>
+        <f>BX20*Insurance!$C$28+BX34</f>
         <v/>
       </c>
       <c r="BY33">
-        <f>BY20*Insurance!$C$28</f>
+        <f>BY20*Insurance!$C$28+BY34</f>
         <v/>
       </c>
       <c r="BZ33">
-        <f>BZ20*Insurance!$C$28</f>
+        <f>BZ20*Insurance!$C$28+BZ34</f>
         <v/>
       </c>
       <c r="CA33">
-        <f>CA20*Insurance!$C$28</f>
+        <f>CA20*Insurance!$C$28+CA34</f>
         <v/>
       </c>
       <c r="CB33">
-        <f>CB20*Insurance!$C$28</f>
+        <f>CB20*Insurance!$C$28+CB34</f>
         <v/>
       </c>
       <c r="CC33">
-        <f>CC20*Insurance!$C$28</f>
+        <f>CC20*Insurance!$C$28+CC34</f>
         <v/>
       </c>
       <c r="CD33">
-        <f>CD20*Insurance!$C$28</f>
+        <f>CD20*Insurance!$C$28+CD34</f>
         <v/>
       </c>
       <c r="CE33">
-        <f>CE20*Insurance!$C$28</f>
+        <f>CE20*Insurance!$C$28+CE34</f>
         <v/>
       </c>
       <c r="CF33">
-        <f>CF20*Insurance!$C$28</f>
+        <f>CF20*Insurance!$C$28+CF34</f>
         <v/>
       </c>
       <c r="CG33">
-        <f>CG20*Insurance!$C$28</f>
+        <f>CG20*Insurance!$C$28+CG34</f>
         <v/>
       </c>
       <c r="CH33">
-        <f>CH20*Insurance!$C$28</f>
+        <f>CH20*Insurance!$C$28+CH34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Claims on included swings ($)</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>C16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>D16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>E16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>F16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>G16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>H16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>I16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>J16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>K16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>L16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>M16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>N16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="O34">
+        <f>O16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="P34">
+        <f>P16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="Q34">
+        <f>Q16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="R34">
+        <f>R16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="S34">
+        <f>S16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="T34">
+        <f>T16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="U34">
+        <f>U16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="V34">
+        <f>V16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="W34">
+        <f>W16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>X16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>Y16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="Z34">
+        <f>Z16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>AA16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>AB16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>AC16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>AD16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>AE16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AF34">
+        <f>AF16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AG34">
+        <f>AG16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AH34">
+        <f>AH16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AI34">
+        <f>AI16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AJ34">
+        <f>AJ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AK34">
+        <f>AK16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AL34">
+        <f>AL16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AM34">
+        <f>AM16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AN34">
+        <f>AN16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AO34">
+        <f>AO16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AP34">
+        <f>AP16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AQ34">
+        <f>AQ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AR34">
+        <f>AR16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AS34">
+        <f>AS16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AT34">
+        <f>AT16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AU34">
+        <f>AU16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AV34">
+        <f>AV16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AW34">
+        <f>AW16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AX34">
+        <f>AX16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AY34">
+        <f>AY16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AZ34">
+        <f>AZ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BA34">
+        <f>BA16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BB34">
+        <f>BB16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BC34">
+        <f>BC16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BD34">
+        <f>BD16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BE34">
+        <f>BE16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BF34">
+        <f>BF16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BG34">
+        <f>BG16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BH34">
+        <f>BH16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BI34">
+        <f>BI16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BJ34">
+        <f>BJ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BK34">
+        <f>BK16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BL34">
+        <f>BL16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BM34">
+        <f>BM16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BN34">
+        <f>BN16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BO34">
+        <f>BO16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BP34">
+        <f>BP16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BQ34">
+        <f>BQ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BR34">
+        <f>BR16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BS34">
+        <f>BS16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BT34">
+        <f>BT16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BU34">
+        <f>BU16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BV34">
+        <f>BV16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BW34">
+        <f>BW16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BX34">
+        <f>BX16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BY34">
+        <f>BY16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BZ34">
+        <f>BZ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CA34">
+        <f>CA16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CB34">
+        <f>CB16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CC34">
+        <f>CC16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CD34">
+        <f>CD16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CE34">
+        <f>CE16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CF34">
+        <f>CF16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CG34">
+        <f>CG16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CH34">
+        <f>CH16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
         <v/>
       </c>
     </row>
@@ -8199,7 +8943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H28"/>
+  <dimension ref="B2:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="2" max="2"/>
@@ -8558,6 +9302,86 @@
       <c r="C28">
         <f>G18</f>
         <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>BLENDED — per member per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Included swings expected claim ($)</t>
+        </is>
+      </c>
+      <c r="C31">
+        <f>Assumptions!C51*Assumptions!C52*C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Premium ceded on membership ($)</t>
+        </is>
+      </c>
+      <c r="C32">
+        <f>Assumptions!C19*Assumptions!C53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Trade-up premium ($)</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Trade-up expected claim ($)</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Blended loss ratio</t>
+        </is>
+      </c>
+      <c r="C35">
+        <f>(C31+C34)/(C32+C33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Counterfactual — 16 swings/mo at $10,000, unlimited</t>
+        </is>
+      </c>
+      <c r="C36">
+        <f>16*10000*C8/(Assumptions!C19*0.24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>A 533% loss ratio. This is why unlimited cannot be written.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8901,31 +9725,31 @@
         </is>
       </c>
       <c r="C18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="D18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="E18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="F18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="G18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="H18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="I18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -9310,35 +10134,35 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Premium ceded (24%)</t>
+          <t>Premium ceded (membership + entries)</t>
         </is>
       </c>
       <c r="C34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="H34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="I34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
